--- a/WIR Photo Tool V1.0.xlsx
+++ b/WIR Photo Tool V1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1. Project\2025\TIDC\Cx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD0B8F38-A6BD-4A91-B478-168918867198}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F6C0A2-548C-4695-AD74-38CAFD5C28DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13866" activeTab="3" xr2:uid="{832FDD36-A949-4CF0-9F6A-C4C419010199}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="147">
   <si>
     <r>
       <rPr>
@@ -555,9 +555,6 @@
   </si>
   <si>
     <t>1. Repaint all scratched surfaces.</t>
-  </si>
-  <si>
-    <t>x</t>
   </si>
 </sst>
 </file>
@@ -22973,16 +22970,12 @@
     </row>
     <row r="12" spans="1:16" ht="19.399999999999999" customHeight="1">
       <c r="A12" s="153"/>
-      <c r="B12" s="55" t="s">
-        <v>147</v>
-      </c>
+      <c r="B12" s="55"/>
       <c r="C12" s="154"/>
       <c r="D12" s="154"/>
       <c r="E12" s="154"/>
       <c r="F12" s="155"/>
-      <c r="G12" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="G12" s="154"/>
       <c r="H12" s="154"/>
       <c r="I12" s="156"/>
       <c r="J12" s="156"/>
@@ -23139,14 +23132,12 @@
     </row>
     <row r="21" spans="1:16" ht="19.399999999999999" customHeight="1">
       <c r="A21" s="162"/>
-      <c r="B21" s="163"/>
+      <c r="B21" s="154"/>
       <c r="C21" s="156"/>
       <c r="D21" s="63"/>
       <c r="E21" s="63"/>
       <c r="F21" s="63"/>
-      <c r="G21" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="G21" s="154"/>
       <c r="H21" s="108"/>
       <c r="I21" s="108"/>
       <c r="J21" s="108"/>
@@ -23159,14 +23150,12 @@
     </row>
     <row r="22" spans="1:16" ht="19.399999999999999" customHeight="1">
       <c r="A22" s="162"/>
-      <c r="B22" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="B22" s="154"/>
       <c r="C22" s="156"/>
       <c r="D22" s="63"/>
       <c r="E22" s="63"/>
       <c r="F22" s="63"/>
-      <c r="G22" s="63"/>
+      <c r="G22" s="154"/>
       <c r="H22" s="108"/>
       <c r="I22" s="108"/>
       <c r="J22" s="108"/>
@@ -23323,16 +23312,12 @@
     </row>
     <row r="31" spans="1:16" ht="19.399999999999999" customHeight="1">
       <c r="A31" s="168"/>
-      <c r="B31" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="B31" s="154"/>
       <c r="C31" s="156"/>
       <c r="D31" s="63"/>
       <c r="E31" s="63"/>
       <c r="F31" s="63"/>
-      <c r="G31" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="G31" s="154"/>
       <c r="H31" s="102"/>
       <c r="I31" s="102"/>
       <c r="J31" s="102"/>
@@ -23949,16 +23934,12 @@
     </row>
     <row r="64" spans="1:16" ht="19.399999999999999" customHeight="1">
       <c r="A64" s="153"/>
-      <c r="B64" s="55" t="s">
-        <v>147</v>
-      </c>
+      <c r="B64" s="55"/>
       <c r="C64" s="154"/>
       <c r="D64" s="154"/>
       <c r="E64" s="154"/>
       <c r="F64" s="155"/>
-      <c r="G64" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="G64" s="154"/>
       <c r="H64" s="154"/>
       <c r="I64" s="156"/>
       <c r="J64" s="156"/>
@@ -24120,9 +24101,7 @@
       <c r="D73" s="63"/>
       <c r="E73" s="63"/>
       <c r="F73" s="63"/>
-      <c r="G73" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="G73" s="154"/>
       <c r="H73" s="108"/>
       <c r="I73" s="108"/>
       <c r="J73" s="108"/>
@@ -24135,9 +24114,7 @@
     </row>
     <row r="74" spans="1:16" ht="19.399999999999999" customHeight="1">
       <c r="A74" s="162"/>
-      <c r="B74" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="B74" s="154"/>
       <c r="C74" s="156"/>
       <c r="D74" s="63"/>
       <c r="E74" s="63"/>
@@ -24299,16 +24276,12 @@
     </row>
     <row r="83" spans="1:16" ht="19.399999999999999" customHeight="1">
       <c r="A83" s="168"/>
-      <c r="B83" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="B83" s="154"/>
       <c r="C83" s="156"/>
       <c r="D83" s="63"/>
       <c r="E83" s="63"/>
       <c r="F83" s="63"/>
-      <c r="G83" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="G83" s="154"/>
       <c r="H83" s="102"/>
       <c r="I83" s="102"/>
       <c r="J83" s="102"/>
@@ -24925,16 +24898,12 @@
     </row>
     <row r="116" spans="1:16" ht="19.399999999999999" customHeight="1">
       <c r="A116" s="153"/>
-      <c r="B116" s="55" t="s">
-        <v>147</v>
-      </c>
+      <c r="B116" s="55"/>
       <c r="C116" s="154"/>
       <c r="D116" s="154"/>
       <c r="E116" s="154"/>
       <c r="F116" s="155"/>
-      <c r="G116" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="G116" s="154"/>
       <c r="H116" s="154"/>
       <c r="I116" s="156"/>
       <c r="J116" s="156"/>
@@ -25096,9 +25065,7 @@
       <c r="D125" s="63"/>
       <c r="E125" s="63"/>
       <c r="F125" s="63"/>
-      <c r="G125" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="G125" s="154"/>
       <c r="H125" s="108"/>
       <c r="I125" s="108"/>
       <c r="J125" s="108"/>
@@ -25111,9 +25078,7 @@
     </row>
     <row r="126" spans="1:16" ht="19.399999999999999" customHeight="1">
       <c r="A126" s="162"/>
-      <c r="B126" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="B126" s="154"/>
       <c r="C126" s="156"/>
       <c r="D126" s="63"/>
       <c r="E126" s="63"/>
@@ -25275,16 +25240,12 @@
     </row>
     <row r="135" spans="1:16" ht="19.399999999999999" customHeight="1">
       <c r="A135" s="168"/>
-      <c r="B135" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="B135" s="154"/>
       <c r="C135" s="156"/>
       <c r="D135" s="63"/>
       <c r="E135" s="63"/>
       <c r="F135" s="63"/>
-      <c r="G135" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="G135" s="154"/>
       <c r="H135" s="102"/>
       <c r="I135" s="102"/>
       <c r="J135" s="102"/>
@@ -25901,16 +25862,12 @@
     </row>
     <row r="168" spans="1:16" ht="19.399999999999999" customHeight="1">
       <c r="A168" s="153"/>
-      <c r="B168" s="55" t="s">
-        <v>147</v>
-      </c>
+      <c r="B168" s="55"/>
       <c r="C168" s="154"/>
       <c r="D168" s="154"/>
       <c r="E168" s="154"/>
       <c r="F168" s="155"/>
-      <c r="G168" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="G168" s="154"/>
       <c r="H168" s="154"/>
       <c r="I168" s="156"/>
       <c r="J168" s="156"/>
@@ -26072,9 +26029,7 @@
       <c r="D177" s="63"/>
       <c r="E177" s="63"/>
       <c r="F177" s="63"/>
-      <c r="G177" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="G177" s="154"/>
       <c r="H177" s="108"/>
       <c r="I177" s="108"/>
       <c r="J177" s="108"/>
@@ -26087,9 +26042,7 @@
     </row>
     <row r="178" spans="1:16" ht="19.399999999999999" customHeight="1">
       <c r="A178" s="162"/>
-      <c r="B178" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="B178" s="154"/>
       <c r="C178" s="156"/>
       <c r="D178" s="63"/>
       <c r="E178" s="63"/>
@@ -26251,16 +26204,12 @@
     </row>
     <row r="187" spans="1:16" ht="19.399999999999999" customHeight="1">
       <c r="A187" s="168"/>
-      <c r="B187" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="B187" s="154"/>
       <c r="C187" s="156"/>
       <c r="D187" s="63"/>
       <c r="E187" s="63"/>
       <c r="F187" s="63"/>
-      <c r="G187" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="G187" s="154"/>
       <c r="H187" s="102"/>
       <c r="I187" s="102"/>
       <c r="J187" s="102"/>
@@ -26877,16 +26826,12 @@
     </row>
     <row r="220" spans="1:16" ht="19.399999999999999" customHeight="1">
       <c r="A220" s="153"/>
-      <c r="B220" s="55" t="s">
-        <v>147</v>
-      </c>
+      <c r="B220" s="55"/>
       <c r="C220" s="154"/>
       <c r="D220" s="154"/>
       <c r="E220" s="154"/>
       <c r="F220" s="155"/>
-      <c r="G220" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="G220" s="154"/>
       <c r="H220" s="154"/>
       <c r="I220" s="156"/>
       <c r="J220" s="156"/>
@@ -27048,9 +26993,7 @@
       <c r="D229" s="63"/>
       <c r="E229" s="63"/>
       <c r="F229" s="63"/>
-      <c r="G229" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="G229" s="154"/>
       <c r="H229" s="108"/>
       <c r="I229" s="108"/>
       <c r="J229" s="108"/>
@@ -27063,9 +27006,7 @@
     </row>
     <row r="230" spans="1:16" ht="19.399999999999999" customHeight="1">
       <c r="A230" s="162"/>
-      <c r="B230" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="B230" s="154"/>
       <c r="C230" s="156"/>
       <c r="D230" s="63"/>
       <c r="E230" s="63"/>
@@ -27227,16 +27168,12 @@
     </row>
     <row r="239" spans="1:16" ht="19.399999999999999" customHeight="1">
       <c r="A239" s="168"/>
-      <c r="B239" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="B239" s="154"/>
       <c r="C239" s="156"/>
       <c r="D239" s="63"/>
       <c r="E239" s="63"/>
       <c r="F239" s="63"/>
-      <c r="G239" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="G239" s="154"/>
       <c r="H239" s="102"/>
       <c r="I239" s="102"/>
       <c r="J239" s="102"/>
@@ -27853,16 +27790,12 @@
     </row>
     <row r="272" spans="1:16" ht="19.399999999999999" customHeight="1">
       <c r="A272" s="153"/>
-      <c r="B272" s="55" t="s">
-        <v>147</v>
-      </c>
+      <c r="B272" s="55"/>
       <c r="C272" s="154"/>
       <c r="D272" s="154"/>
       <c r="E272" s="154"/>
       <c r="F272" s="155"/>
-      <c r="G272" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="G272" s="154"/>
       <c r="H272" s="154"/>
       <c r="I272" s="156"/>
       <c r="J272" s="156"/>
@@ -28024,9 +27957,7 @@
       <c r="D281" s="63"/>
       <c r="E281" s="63"/>
       <c r="F281" s="63"/>
-      <c r="G281" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="G281" s="154"/>
       <c r="H281" s="108"/>
       <c r="I281" s="108"/>
       <c r="J281" s="108"/>
@@ -28039,9 +27970,7 @@
     </row>
     <row r="282" spans="1:16" ht="19.399999999999999" customHeight="1">
       <c r="A282" s="162"/>
-      <c r="B282" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="B282" s="154"/>
       <c r="C282" s="156"/>
       <c r="D282" s="63"/>
       <c r="E282" s="63"/>
@@ -28203,16 +28132,12 @@
     </row>
     <row r="291" spans="1:16" ht="19.399999999999999" customHeight="1">
       <c r="A291" s="168"/>
-      <c r="B291" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="B291" s="154"/>
       <c r="C291" s="156"/>
       <c r="D291" s="63"/>
       <c r="E291" s="63"/>
       <c r="F291" s="63"/>
-      <c r="G291" s="154" t="s">
-        <v>147</v>
-      </c>
+      <c r="G291" s="154"/>
       <c r="H291" s="102"/>
       <c r="I291" s="102"/>
       <c r="J291" s="102"/>
